--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>BRAKE</t>
   </si>
@@ -80,12 +80,15 @@
     <t>Failed</t>
   </si>
   <si>
-    <t/>
+    <t>Game Over</t>
   </si>
   <si>
     <t>GameOverUIForm.Back</t>
   </si>
   <si>
+    <t>return</t>
+  </si>
+  <si>
     <t>Level.DisplayName1</t>
   </si>
   <si>
@@ -234,6 +237,9 @@
   </si>
   <si>
     <t>Victory</t>
+  </si>
+  <si>
+    <t>Game victory</t>
   </si>
 </sst>
 </file>
@@ -415,6 +421,502 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -4022,250 +4524,250 @@
         <v>6</v>
       </c>
       <c r="C4" s="0" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1"/>
       <c r="B5" s="0" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="0" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1"/>
       <c r="B6" s="0" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1"/>
       <c r="B7" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1"/>
       <c r="B8" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1"/>
       <c r="B9" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1"/>
       <c r="B10" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1"/>
       <c r="B11" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1"/>
       <c r="B12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1"/>
       <c r="B13" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1"/>
       <c r="B14" s="0" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="0" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1"/>
       <c r="B15" s="0" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="0" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1"/>
       <c r="B16" s="0" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1"/>
       <c r="B17" s="0" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C17" s="0" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1"/>
       <c r="B18" s="0" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C18" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1"/>
       <c r="B19" s="0" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C19" s="0" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1"/>
       <c r="B20" s="0" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C20" s="0" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1"/>
       <c r="B21" s="0" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" s="0" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1"/>
       <c r="B22" s="0" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C22" s="0" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1"/>
       <c r="B23" s="0" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C23" s="0" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1"/>
       <c r="B24" s="0" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C24" s="0" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1"/>
       <c r="B25" s="0" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C25" s="0" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1"/>
       <c r="B26" s="0" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" s="0" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1"/>
       <c r="B27" s="0" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C27" s="0" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1"/>
       <c r="B28" s="0" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C28" s="0" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1"/>
       <c r="B29" s="0" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="0" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1"/>
       <c r="B30" s="0" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="0" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1"/>
       <c r="B31" s="0" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C31" s="0" t="s">
-        <v>5</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -4280,7 +4782,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId150" name="A1">
+            <control shapeId="1056" r:id="rId270" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4302,7 +4804,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId151" name="A2">
+            <control shapeId="1057" r:id="rId271" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4324,7 +4826,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId152" name="A3">
+            <control shapeId="1058" r:id="rId272" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4346,7 +4848,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId153" name="A4">
+            <control shapeId="1059" r:id="rId273" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4368,7 +4870,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId154" name="A5">
+            <control shapeId="1060" r:id="rId274" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4390,7 +4892,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId155" name="A6">
+            <control shapeId="1061" r:id="rId275" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4412,7 +4914,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId156" name="A7">
+            <control shapeId="1062" r:id="rId276" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4434,7 +4936,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId157" name="A8">
+            <control shapeId="1063" r:id="rId277" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4456,7 +4958,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId158" name="A9">
+            <control shapeId="1064" r:id="rId278" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4478,7 +4980,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId159" name="A10">
+            <control shapeId="1065" r:id="rId279" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4500,7 +5002,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId160" name="A11">
+            <control shapeId="1066" r:id="rId280" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4522,7 +5024,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId161" name="A12">
+            <control shapeId="1067" r:id="rId281" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4544,7 +5046,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId162" name="A13">
+            <control shapeId="1068" r:id="rId282" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4566,7 +5068,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId163" name="A14">
+            <control shapeId="1069" r:id="rId283" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4588,7 +5090,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId164" name="A15">
+            <control shapeId="1070" r:id="rId284" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4610,7 +5112,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1071" r:id="rId165" name="A16">
+            <control shapeId="1071" r:id="rId285" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4632,7 +5134,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1072" r:id="rId166" name="A17">
+            <control shapeId="1072" r:id="rId286" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4654,7 +5156,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1073" r:id="rId167" name="A18">
+            <control shapeId="1073" r:id="rId287" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4676,7 +5178,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1074" r:id="rId168" name="A19">
+            <control shapeId="1074" r:id="rId288" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4698,7 +5200,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1075" r:id="rId169" name="A20">
+            <control shapeId="1075" r:id="rId289" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4720,7 +5222,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1076" r:id="rId170" name="A21">
+            <control shapeId="1076" r:id="rId290" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4742,7 +5244,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1077" r:id="rId171" name="A22">
+            <control shapeId="1077" r:id="rId291" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4764,7 +5266,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1078" r:id="rId172" name="A23">
+            <control shapeId="1078" r:id="rId292" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4786,7 +5288,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1079" r:id="rId173" name="A24">
+            <control shapeId="1079" r:id="rId293" name="A24">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4808,7 +5310,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1080" r:id="rId174" name="A25">
+            <control shapeId="1080" r:id="rId294" name="A25">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4830,7 +5332,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1081" r:id="rId175" name="A26">
+            <control shapeId="1081" r:id="rId295" name="A26">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4852,7 +5354,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1082" r:id="rId176" name="A27">
+            <control shapeId="1082" r:id="rId296" name="A27">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4874,7 +5376,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1083" r:id="rId177" name="A28">
+            <control shapeId="1083" r:id="rId297" name="A28">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4896,7 +5398,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1084" r:id="rId178" name="A29">
+            <control shapeId="1084" r:id="rId298" name="A29">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4918,7 +5420,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1085" r:id="rId179" name="A30">
+            <control shapeId="1085" r:id="rId299" name="A30">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4940,7 +5442,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1086" r:id="rId180" name="A31">
+            <control shapeId="1086" r:id="rId300" name="A31">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -63,12 +63,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>NoSaveData</t>
   </si>
   <si>
-    <t/>
+    <t>No archived data</t>
   </si>
   <si>
     <t>Nothing</t>
@@ -93,6 +93,30 @@
   </si>
   <si>
     <t>Open Save List</t>
+  </si>
+  <si>
+    <t>scene.base.name</t>
+  </si>
+  <si>
+    <t>base</t>
+  </si>
+  <si>
+    <t>scene.menu.name</t>
+  </si>
+  <si>
+    <t>Main Menu</t>
+  </si>
+  <si>
+    <t>scene.tutorial.name</t>
+  </si>
+  <si>
+    <t>A certain laboratory</t>
+  </si>
+  <si>
+    <t>scene.world.name</t>
+  </si>
+  <si>
+    <t>the big world</t>
   </si>
   <si>
     <t>Settings.Help</t>
@@ -176,7 +200,7 @@
     <t>UI_Welcome</t>
   </si>
   <si>
-    <t>Welcome, {0}!</t>
+    <t>Welcome</t>
   </si>
 </sst>
 </file>
@@ -253,7 +277,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -261,7 +285,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp16.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp17.xml><?xml version="1.0" encoding="utf-8"?>
@@ -277,6 +301,22 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -2119,6 +2159,634 @@
     <mc:Fallback/>
   </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
       <xdr:twoCellAnchor editAs="oneCell">
         <xdr:from>
@@ -2135,351 +2803,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1044">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1044"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1045">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1045"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1046">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1046"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1047">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1047"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1048">
+            <xdr:cNvPr hidden="1" name="A1" id="1048">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1048"/>
@@ -2554,18 +2878,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1049">
+            <xdr:cNvPr hidden="1" name="A2" id="1049">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1049"/>
@@ -2640,18 +2964,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1050">
+            <xdr:cNvPr hidden="1" name="A3" id="1050">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1050"/>
@@ -2726,18 +3050,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1051">
+            <xdr:cNvPr hidden="1" name="A4" id="1051">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1051"/>
@@ -2812,18 +3136,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1052">
+            <xdr:cNvPr hidden="1" name="A5" id="1052">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1052"/>
@@ -2898,18 +3222,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1053">
+            <xdr:cNvPr hidden="1" name="A6" id="1053">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1053"/>
@@ -2984,18 +3308,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1054">
+            <xdr:cNvPr hidden="1" name="A7" id="1054">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1054"/>
@@ -3070,18 +3394,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1055">
+            <xdr:cNvPr hidden="1" name="A8" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -3156,18 +3480,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1056">
+            <xdr:cNvPr hidden="1" name="A9" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -3242,18 +3566,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1057">
+            <xdr:cNvPr hidden="1" name="A10" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -3328,18 +3652,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1058">
+            <xdr:cNvPr hidden="1" name="A11" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -3414,18 +3738,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1059">
+            <xdr:cNvPr hidden="1" name="A12" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -3500,18 +3824,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1060">
+            <xdr:cNvPr hidden="1" name="A13" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -3586,18 +3910,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1061">
+            <xdr:cNvPr hidden="1" name="A14" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -3672,6 +3996,350 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>14</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A15" id="1062">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1062"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1063">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1063"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1064">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1064"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1065">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1065"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>18</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -3683,10 +4351,354 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1062">
+            <xdr:cNvPr hidden="1" name="A19" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1062"/>
+                  <a14:compatExt spid="_x0000_s1066"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1067">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1067"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1068">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1068"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1069">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1069"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A23" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -4052,7 +5064,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -4231,6 +5243,42 @@
         <v>37</v>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1"/>
+      <c r="B20" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1"/>
+      <c r="B21" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1"/>
+      <c r="B22" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1"/>
+      <c r="B23" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4243,7 +5291,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1044" r:id="rId438" name="A1">
+            <control shapeId="1048" r:id="rId588" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4265,7 +5313,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1045" r:id="rId439" name="A2">
+            <control shapeId="1049" r:id="rId589" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4287,7 +5335,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1046" r:id="rId440" name="A3">
+            <control shapeId="1050" r:id="rId590" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4309,7 +5357,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1047" r:id="rId441" name="A4">
+            <control shapeId="1051" r:id="rId591" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4331,7 +5379,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId442" name="A5">
+            <control shapeId="1052" r:id="rId592" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4353,7 +5401,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId443" name="A6">
+            <control shapeId="1053" r:id="rId593" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4375,7 +5423,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId444" name="A7">
+            <control shapeId="1054" r:id="rId594" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4397,7 +5445,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId445" name="A8">
+            <control shapeId="1055" r:id="rId595" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4419,7 +5467,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId446" name="A9">
+            <control shapeId="1056" r:id="rId596" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4441,7 +5489,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId447" name="A10">
+            <control shapeId="1057" r:id="rId597" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4463,7 +5511,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId448" name="A11">
+            <control shapeId="1058" r:id="rId598" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4485,7 +5533,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId449" name="A12">
+            <control shapeId="1059" r:id="rId599" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4507,7 +5555,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId450" name="A13">
+            <control shapeId="1060" r:id="rId600" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4529,7 +5577,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId451" name="A14">
+            <control shapeId="1061" r:id="rId601" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4551,7 +5599,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId452" name="A15">
+            <control shapeId="1062" r:id="rId602" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4573,7 +5621,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId453" name="A16">
+            <control shapeId="1063" r:id="rId603" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4595,7 +5643,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId454" name="A17">
+            <control shapeId="1064" r:id="rId604" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4617,7 +5665,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId455" name="A18">
+            <control shapeId="1065" r:id="rId605" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4639,7 +5687,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId456" name="A19">
+            <control shapeId="1066" r:id="rId606" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -4659,6 +5707,94 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1067" r:id="rId607" name="A20">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>19</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1068" r:id="rId608" name="A21">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>20</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1069" r:id="rId609" name="A22">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>21</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1070" r:id="rId610" name="A23">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>22</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>

--- a/AAAGameData/Languages/English.xlsx
+++ b/AAAGameData/Languages/English.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
   <si>
     <t>NoSaveData</t>
   </si>
@@ -95,16 +95,58 @@
     <t>Open Save List</t>
   </si>
   <si>
+    <t>scene.abyss.name</t>
+  </si>
+  <si>
+    <t>The Abyssal Land</t>
+  </si>
+  <si>
+    <t>scene.avalon.name</t>
+  </si>
+  <si>
+    <t>Avalon</t>
+  </si>
+  <si>
+    <t>scene.babylon.name</t>
+  </si>
+  <si>
+    <t>hanging gardens of babylon</t>
+  </si>
+  <si>
     <t>scene.base.name</t>
   </si>
   <si>
     <t>base</t>
   </si>
   <si>
+    <t>scene.herheim.name</t>
+  </si>
+  <si>
+    <t>Herheimer</t>
+  </si>
+  <si>
     <t>scene.menu.name</t>
   </si>
   <si>
     <t>Main Menu</t>
+  </si>
+  <si>
+    <t>scene.olympus.name</t>
+  </si>
+  <si>
+    <t>Mount Olympus</t>
+  </si>
+  <si>
+    <t>scene.takamahara.name</t>
+  </si>
+  <si>
+    <t>Takamagahara</t>
+  </si>
+  <si>
+    <t>scene.tiangong.name</t>
+  </si>
+  <si>
+    <t>Heavenly Palace</t>
   </si>
   <si>
     <t>scene.tutorial.name</t>
@@ -261,7 +303,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp10.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp11.xml><?xml version="1.0" encoding="utf-8"?>
@@ -269,15 +311,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp12.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp13.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp14.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp15.xml><?xml version="1.0" encoding="utf-8"?>
@@ -293,7 +335,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp18.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp19.xml><?xml version="1.0" encoding="utf-8"?>
@@ -305,7 +347,7 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp20.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp21.xml><?xml version="1.0" encoding="utf-8"?>
@@ -313,14 +355,42 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp22.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp23.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
+<file path=xl/ctrlProps/ctrlProp24.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp25.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp26.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp27.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp28.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp29.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp3.xml><?xml version="1.0" encoding="utf-8"?>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+</file>
+
+<file path=xl/ctrlProps/ctrlProp30.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
 </file>
 
@@ -333,15 +403,15 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp6.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp7.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp8.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="CheckBox" lockText="1" noThreeD="1" checked="Checked"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp9.xml><?xml version="1.0" encoding="utf-8"?>
@@ -350,6 +420,338 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
+    <mc:Fallback/>
+  </mc:AlternateContent>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14"/>
     <mc:Fallback/>
@@ -2803,609 +3205,7 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A1" id="1048">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1048"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>1</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A2" id="1049">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1049"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>2</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A3" id="1050">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1050"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>3</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A4" id="1051">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1051"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>4</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A5" id="1052">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1052"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>5</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A6" id="1053">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1053"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>6</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A7" id="1054">
-              <a:extLst>
-                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1054"/>
-                </a:ext>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr/>
-          </xdr:nvSpPr>
-          <xdr:spPr bwMode="auto">
-            <a:xfrm>
-              <a:off y="0" x="0"/>
-              <a:ext cy="0" cx="0"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:extLst>
-              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-                <a14:hiddenFill>
-                  <a:solidFill>
-                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
-                  </a:solidFill>
-                </a14:hiddenFill>
-              </a:ext>
-              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-                <a14:hiddenLine w="9525">
-                  <a:solidFill>
-                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
-                  </a:solidFill>
-                  <a:miter lim="800000"/>
-                  <a:headEnd/>
-                  <a:tailEnd/>
-                </a14:hiddenLine>
-              </a:ext>
-            </a:extLst>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr rtl="0" algn="l">
-                <a:defRPr sz="1000"/>
-              </a:pPr>
-              <a:r>
-                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
-                  <a:solidFill>
-                    <a:srgbClr val="000000"/>
-                  </a:solidFill>
-                  <a:latin typeface="Segoe UI"/>
-                  <a:cs typeface="Segoe UI"/>
-                </a:rPr>
-                <a:t>锁定</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-        <xdr:clientData fPrintsWithSheet="0"/>
-      </xdr:twoCellAnchor>
-    </mc:Choice>
-    <mc:Fallback/>
-  </mc:AlternateContent>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-      <xdr:twoCellAnchor editAs="oneCell">
-        <xdr:from>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>0</xdr:colOff>
-          <xdr:row>7</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:from>
-        <xdr:to>
-          <xdr:col>0</xdr:col>
-          <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>8</xdr:row>
-          <xdr:rowOff>0</xdr:rowOff>
-        </xdr:to>
-        <xdr:sp macro="" textlink="" fLocksText="1">
-          <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A8" id="1055">
+            <xdr:cNvPr hidden="1" name="A1" id="1055">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1055"/>
@@ -3480,18 +3280,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>8</xdr:row>
+          <xdr:row>1</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A9" id="1056">
+            <xdr:cNvPr hidden="1" name="A2" id="1056">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1056"/>
@@ -3566,18 +3366,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>9</xdr:row>
+          <xdr:row>2</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A10" id="1057">
+            <xdr:cNvPr hidden="1" name="A3" id="1057">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1057"/>
@@ -3652,18 +3452,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>10</xdr:row>
+          <xdr:row>3</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A11" id="1058">
+            <xdr:cNvPr hidden="1" name="A4" id="1058">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1058"/>
@@ -3738,18 +3538,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>11</xdr:row>
+          <xdr:row>4</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A12" id="1059">
+            <xdr:cNvPr hidden="1" name="A5" id="1059">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1059"/>
@@ -3824,18 +3624,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>12</xdr:row>
+          <xdr:row>5</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A13" id="1060">
+            <xdr:cNvPr hidden="1" name="A6" id="1060">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1060"/>
@@ -3910,18 +3710,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>13</xdr:row>
+          <xdr:row>6</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A14" id="1061">
+            <xdr:cNvPr hidden="1" name="A7" id="1061">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1061"/>
@@ -3996,18 +3796,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>14</xdr:row>
+          <xdr:row>7</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A15" id="1062">
+            <xdr:cNvPr hidden="1" name="A8" id="1062">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1062"/>
@@ -4082,18 +3882,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>15</xdr:row>
+          <xdr:row>8</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A16" id="1063">
+            <xdr:cNvPr hidden="1" name="A9" id="1063">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1063"/>
@@ -4168,18 +3968,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>16</xdr:row>
+          <xdr:row>9</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A17" id="1064">
+            <xdr:cNvPr hidden="1" name="A10" id="1064">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1064"/>
@@ -4254,18 +4054,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>17</xdr:row>
+          <xdr:row>10</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A18" id="1065">
+            <xdr:cNvPr hidden="1" name="A11" id="1065">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1065"/>
@@ -4340,18 +4140,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>18</xdr:row>
+          <xdr:row>11</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A19" id="1066">
+            <xdr:cNvPr hidden="1" name="A12" id="1066">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1066"/>
@@ -4426,18 +4226,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>19</xdr:row>
+          <xdr:row>12</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A20" id="1067">
+            <xdr:cNvPr hidden="1" name="A13" id="1067">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1067"/>
@@ -4512,18 +4312,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>20</xdr:row>
+          <xdr:row>13</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A21" id="1068">
+            <xdr:cNvPr hidden="1" name="A14" id="1068">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1068"/>
@@ -4598,18 +4398,18 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
-          <xdr:row>21</xdr:row>
+          <xdr:row>14</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
           <xdr:colOff>285750</xdr:colOff>
-          <xdr:row>22</xdr:row>
+          <xdr:row>15</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A22" id="1069">
+            <xdr:cNvPr hidden="1" name="A15" id="1069">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
                   <a14:compatExt spid="_x0000_s1069"/>
@@ -4684,6 +4484,608 @@
         <xdr:from>
           <xdr:col>0</xdr:col>
           <xdr:colOff>0</xdr:colOff>
+          <xdr:row>15</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A16" id="1070">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1070"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>16</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A17" id="1071">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1071"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>17</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A18" id="1072">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1072"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>18</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A19" id="1073">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1073"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>19</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A20" id="1074">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1074"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>20</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A21" id="1075">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1075"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>21</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>22</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A22" id="1076">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1076"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
           <xdr:row>22</xdr:row>
           <xdr:rowOff>0</xdr:rowOff>
         </xdr:from>
@@ -4695,10 +5097,612 @@
         </xdr:to>
         <xdr:sp macro="" textlink="" fLocksText="1">
           <xdr:nvSpPr>
-            <xdr:cNvPr hidden="1" name="A23" id="1070">
+            <xdr:cNvPr hidden="1" name="A23" id="1077">
               <a:extLst>
                 <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
-                  <a14:compatExt spid="_x0000_s1070"/>
+                  <a14:compatExt spid="_x0000_s1077"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>23</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A24" id="1078">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1078"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>24</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A25" id="1079">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1079"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>25</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A26" id="1080">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1080"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>26</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A27" id="1081">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1081"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>27</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A28" id="1082">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1082"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>28</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A29" id="1083">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1083"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off y="0" x="0"/>
+              <a:ext cy="0" cx="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+                <a14:hiddenFill>
+                  <a:solidFill>
+                    <a:srgbClr val="FFFFFF" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="65"/>
+                  </a:solidFill>
+                </a14:hiddenFill>
+              </a:ext>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:solidFill>
+                    <a:srgbClr val="000000" mc:Ignorable="a14" a14:legacySpreadsheetColorIndex="64"/>
+                  </a:solidFill>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr upright="1" anchor="ctr" bIns="27432" rIns="27432" tIns="27432" lIns="27432" wrap="square" vertOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr rtl="0" algn="l">
+                <a:defRPr sz="1000"/>
+              </a:pPr>
+              <a:r>
+                <a:rPr lang="en-US" sz="800" baseline="0" strike="noStrike" u="none" i="0" b="0">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI"/>
+                  <a:cs typeface="Segoe UI"/>
+                </a:rPr>
+                <a:t>锁定</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+        <xdr:clientData fPrintsWithSheet="0"/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>0</xdr:colOff>
+          <xdr:row>29</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>0</xdr:col>
+          <xdr:colOff>285750</xdr:colOff>
+          <xdr:row>30</xdr:row>
+          <xdr:rowOff>0</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="" fLocksText="1">
+          <xdr:nvSpPr>
+            <xdr:cNvPr hidden="1" name="A30" id="1084">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s1084"/>
                 </a:ext>
                 <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
                   <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000001040000}"/>
@@ -5064,11 +6068,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
-    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="2" max="2" width="22.2728118896484" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5279,6 +6283,69 @@
         <v>45</v>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1"/>
+      <c r="B24" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C25" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1"/>
+      <c r="B26" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1"/>
+      <c r="B27" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1"/>
+      <c r="B28" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C28" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1"/>
+      <c r="B29" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C29" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1"/>
+      <c r="B30" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C30" s="0" t="s">
+        <v>59</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5291,7 +6358,7 @@
       <controls>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1048" r:id="rId588" name="A1">
+            <control shapeId="1055" r:id="rId668" name="A1">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5313,7 +6380,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1049" r:id="rId589" name="A2">
+            <control shapeId="1056" r:id="rId669" name="A2">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5335,7 +6402,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1050" r:id="rId590" name="A3">
+            <control shapeId="1057" r:id="rId670" name="A3">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5357,7 +6424,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1051" r:id="rId591" name="A4">
+            <control shapeId="1058" r:id="rId671" name="A4">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5379,7 +6446,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1052" r:id="rId592" name="A5">
+            <control shapeId="1059" r:id="rId672" name="A5">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5401,7 +6468,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1053" r:id="rId593" name="A6">
+            <control shapeId="1060" r:id="rId673" name="A6">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5423,7 +6490,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1054" r:id="rId594" name="A7">
+            <control shapeId="1061" r:id="rId674" name="A7">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5445,7 +6512,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1055" r:id="rId595" name="A8">
+            <control shapeId="1062" r:id="rId675" name="A8">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5467,7 +6534,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1056" r:id="rId596" name="A9">
+            <control shapeId="1063" r:id="rId676" name="A9">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5489,7 +6556,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1057" r:id="rId597" name="A10">
+            <control shapeId="1064" r:id="rId677" name="A10">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5511,7 +6578,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1058" r:id="rId598" name="A11">
+            <control shapeId="1065" r:id="rId678" name="A11">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5533,7 +6600,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1059" r:id="rId599" name="A12">
+            <control shapeId="1066" r:id="rId679" name="A12">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5555,7 +6622,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1060" r:id="rId600" name="A13">
+            <control shapeId="1067" r:id="rId680" name="A13">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5577,7 +6644,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1061" r:id="rId601" name="A14">
+            <control shapeId="1068" r:id="rId681" name="A14">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5599,7 +6666,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1062" r:id="rId602" name="A15">
+            <control shapeId="1069" r:id="rId682" name="A15">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5621,7 +6688,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1063" r:id="rId603" name="A16">
+            <control shapeId="1070" r:id="rId683" name="A16">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5643,7 +6710,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1064" r:id="rId604" name="A17">
+            <control shapeId="1071" r:id="rId684" name="A17">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5665,7 +6732,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1065" r:id="rId605" name="A18">
+            <control shapeId="1072" r:id="rId685" name="A18">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5687,7 +6754,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1066" r:id="rId606" name="A19">
+            <control shapeId="1073" r:id="rId686" name="A19">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5709,7 +6776,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1067" r:id="rId607" name="A20">
+            <control shapeId="1074" r:id="rId687" name="A20">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5731,7 +6798,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1068" r:id="rId608" name="A21">
+            <control shapeId="1075" r:id="rId688" name="A21">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5753,7 +6820,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1069" r:id="rId609" name="A22">
+            <control shapeId="1076" r:id="rId689" name="A22">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5775,7 +6842,7 @@
         </mc:AlternateContent>
         <mc:AlternateContent>
           <mc:Choice Requires="x14">
-            <control shapeId="1070" r:id="rId610" name="A23">
+            <control shapeId="1077" r:id="rId690" name="A23">
               <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
                 <anchor moveWithCells="1">
                   <from>
@@ -5795,6 +6862,160 @@
             </control>
           </mc:Choice>
         </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1078" r:id="rId691" name="A24">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>23</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1079" r:id="rId692" name="A25">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>24</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1080" r:id="rId693" name="A26">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>25</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1081" r:id="rId694" name="A27">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>26</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1082" r:id="rId695" name="A28">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>27</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1083" r:id="rId696" name="A29">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>28</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
+        <mc:AlternateContent>
+          <mc:Choice Requires="x14">
+            <control shapeId="1084" r:id="rId697" name="A30">
+              <controlPr defaultSize="0" print="0" autoFill="0" autoPict="0">
+                <anchor moveWithCells="1">
+                  <from>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>0</xdr:colOff>
+                    <xdr:row>29</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </from>
+                  <to>
+                    <xdr:col>0</xdr:col>
+                    <xdr:colOff>285750</xdr:colOff>
+                    <xdr:row>30</xdr:row>
+                    <xdr:rowOff>0</xdr:rowOff>
+                  </to>
+                </anchor>
+              </controlPr>
+            </control>
+          </mc:Choice>
+        </mc:AlternateContent>
       </controls>
     </mc:Choice>
   </mc:AlternateContent>
